--- a/9432.T_report.xlsx
+++ b/9432.T_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,58 +449,668 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>手数料込み利益率(%)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>手数料(円)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>決済後資産(円)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>保有日数</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>決済理由</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>バックテスト結果</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="I2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2022-01-05</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2022-01-27</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>113.28</v>
+      </c>
+      <c r="E2" t="n">
+        <v>110.39</v>
+      </c>
+      <c r="F2" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="G2" t="n">
+        <v>-2.75</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1974</v>
+      </c>
+      <c r="I2" t="n">
+        <v>972498</v>
+      </c>
+      <c r="J2" t="n">
+        <v>22</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>総取引回数</t>
         </is>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
+      <c r="M2" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="3">
-      <c r="I3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2022-02-03</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2022-02-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>115.78</v>
+      </c>
+      <c r="E3" t="n">
+        <v>112.85</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-2.53</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-2.73</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1920</v>
+      </c>
+      <c r="I3" t="n">
+        <v>945955</v>
+      </c>
+      <c r="J3" t="n">
+        <v>22</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>勝率</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.0%</t>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>42.9%</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="I4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2022-03-07</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2022-03-23</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>117.14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>126.52</v>
+      </c>
+      <c r="F4" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="G4" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1968</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1019815</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>総利益率</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>7.61%</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="I5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2022-04-28</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="E5" t="n">
+        <v>135.38</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2102</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1080394</v>
+      </c>
+      <c r="J5" t="n">
+        <v>23</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>平均保有日数</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.0日</t>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>18.9日</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2022-05-31</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2022-06-15</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>137.91</v>
+      </c>
+      <c r="E6" t="n">
+        <v>134.58</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.42</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2135</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1052115</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>最終資産</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1076120</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2022-11-09</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>141.53</v>
+      </c>
+      <c r="E7" t="n">
+        <v>140.07</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1.23</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2093</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1039150</v>
+      </c>
+      <c r="J7" t="n">
+        <v>28</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>手数料込み利益</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>76120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>142.78</v>
+      </c>
+      <c r="E8" t="n">
+        <v>151.68</v>
+      </c>
+      <c r="F8" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="G8" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2143</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1101772</v>
+      </c>
+      <c r="J8" t="n">
+        <v>52</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>総手数料</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>29309</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2023-05-12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2023-05-30</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>149.37</v>
+      </c>
+      <c r="E9" t="n">
+        <v>145.7</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-2.46</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-2.66</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2176</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1072501</v>
+      </c>
+      <c r="J9" t="n">
+        <v>18</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2023-06-27</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2023-06-30</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>152.21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>154.68</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2162</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1087757</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2024-03-22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2024-04-01</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>169.11</v>
+      </c>
+      <c r="E11" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-2.72</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2148</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1058190</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-01-06</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025-01-10</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>149.33</v>
+      </c>
+      <c r="E12" t="n">
+        <v>145.9</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2092</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1031786</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>148.19</v>
+      </c>
+      <c r="E13" t="n">
+        <v>149.44</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2072</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1038413</v>
+      </c>
+      <c r="J13" t="n">
+        <v>30</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>148.19</v>
+      </c>
+      <c r="E14" t="n">
+        <v>157.46</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G14" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2142</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1101210</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-01-07</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>156.7</v>
+      </c>
+      <c r="E15" t="n">
+        <v>153.44</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-2.08</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-2.28</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2180</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1076120</v>
+      </c>
+      <c r="J15" t="n">
+        <v>15</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>atr_stop</t>
         </is>
       </c>
     </row>

--- a/9432.T_report.xlsx
+++ b/9432.T_report.xlsx
@@ -557,7 +557,7 @@
         <v>1920</v>
       </c>
       <c r="I3" t="n">
-        <v>945955</v>
+        <v>945956</v>
       </c>
       <c r="J3" t="n">
         <v>22</v>
@@ -625,7 +625,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>7.61%</t>
+          <t>6.93%</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>18.9日</t>
+          <t>19.4日</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>1076120</v>
+        <v>1069303</v>
       </c>
     </row>
     <row r="7">
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>76120</v>
+        <v>69303</v>
       </c>
     </row>
     <row r="8">
@@ -824,7 +824,7 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>29309</v>
+        <v>29261</v>
       </c>
     </row>
     <row r="9">
@@ -956,7 +956,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2025-01-06</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -965,25 +965,25 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>149.33</v>
+        <v>150.28</v>
       </c>
       <c r="E12" t="n">
         <v>145.9</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3</v>
+        <v>-2.92</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.5</v>
+        <v>-3.11</v>
       </c>
       <c r="H12" t="n">
-        <v>2092</v>
+        <v>2086</v>
       </c>
       <c r="I12" t="n">
-        <v>1031786</v>
+        <v>1025249</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1018,10 +1018,10 @@
         <v>0.64</v>
       </c>
       <c r="H13" t="n">
-        <v>2072</v>
+        <v>2059</v>
       </c>
       <c r="I13" t="n">
-        <v>1038413</v>
+        <v>1031834</v>
       </c>
       <c r="J13" t="n">
         <v>30</v>
@@ -1059,10 +1059,10 @@
         <v>6.05</v>
       </c>
       <c r="H14" t="n">
-        <v>2142</v>
+        <v>2128</v>
       </c>
       <c r="I14" t="n">
-        <v>1101210</v>
+        <v>1094233</v>
       </c>
       <c r="J14" t="n">
         <v>6</v>
@@ -1100,10 +1100,10 @@
         <v>-2.28</v>
       </c>
       <c r="H15" t="n">
-        <v>2180</v>
+        <v>2166</v>
       </c>
       <c r="I15" t="n">
-        <v>1076120</v>
+        <v>1069303</v>
       </c>
       <c r="J15" t="n">
         <v>15</v>
